--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Flexicap Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Flexicap Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="206">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Flexicap Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -52,7 +52,7 @@
     <t>Yield to Call @</t>
   </si>
   <si>
-    <t>Equity &amp; Equity Related Instruments</t>
+    <t>Equity &amp; Equity Related Instruments (Note -1)</t>
   </si>
   <si>
     <t/>
@@ -70,21 +70,21 @@
     <t>Automobiles</t>
   </si>
   <si>
+    <t>ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE090A01021</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
     <t>Maruti Suzuki India Ltd.</t>
   </si>
   <si>
     <t>INE585B01010</t>
   </si>
   <si>
-    <t>ICICI Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE090A01021</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
     <t>Avenue Supermarts Ltd.</t>
   </si>
   <si>
@@ -115,22 +115,70 @@
     <t>INE758T01015</t>
   </si>
   <si>
+    <t>PI Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE603J01030</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agrochemicals</t>
+  </si>
+  <si>
+    <t>The Ethos Ltd.</t>
+  </si>
+  <si>
+    <t>INE04TZ01018</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Larsen &amp; Toubro Ltd.</t>
+  </si>
+  <si>
+    <t>INE018A01030</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Azad Engineering Ltd</t>
+  </si>
+  <si>
+    <t>INE02IJ01035</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Axis Bank Ltd.</t>
+  </si>
+  <si>
+    <t>INE238A01034</t>
+  </si>
+  <si>
+    <t>Bharti Airtel Ltd.</t>
+  </si>
+  <si>
+    <t>INE397D01024</t>
+  </si>
+  <si>
+    <t>Telecom - Services</t>
+  </si>
+  <si>
     <t>Red Tape Ltd</t>
   </si>
   <si>
     <t>INE0LXT01019</t>
   </si>
   <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Larsen &amp; Toubro Ltd.</t>
-  </si>
-  <si>
-    <t>INE018A01030</t>
-  </si>
-  <si>
-    <t>Construction</t>
+    <t>RR Kabel Ltd.</t>
+  </si>
+  <si>
+    <t>INE777K01022</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
   </si>
   <si>
     <t>Eicher Motors Ltd.</t>
@@ -139,34 +187,13 @@
     <t>INE066A01021</t>
   </si>
   <si>
-    <t>The Ethos Ltd.</t>
-  </si>
-  <si>
-    <t>INE04TZ01018</t>
-  </si>
-  <si>
-    <t>PI Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE603J01030</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agrochemicals</t>
-  </si>
-  <si>
-    <t>Axis Bank Ltd.</t>
-  </si>
-  <si>
-    <t>INE238A01034</t>
-  </si>
-  <si>
-    <t>Bharti Airtel Ltd.</t>
-  </si>
-  <si>
-    <t>INE397D01024</t>
-  </si>
-  <si>
-    <t>Telecom - Services</t>
+    <t>Samvardhana Motherson International Ltd.</t>
+  </si>
+  <si>
+    <t>INE775A01035</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
   </si>
   <si>
     <t>State Bank Of India</t>
@@ -175,22 +202,28 @@
     <t>INE062A01020</t>
   </si>
   <si>
-    <t>Samvardhana Motherson International Ltd.</t>
-  </si>
-  <si>
-    <t>INE775A01035</t>
-  </si>
-  <si>
-    <t>Auto Components</t>
-  </si>
-  <si>
-    <t>Azad Engineering Ltd</t>
-  </si>
-  <si>
-    <t>INE02IJ01035</t>
-  </si>
-  <si>
-    <t>Electrical Equipment</t>
+    <t>Interglobe Aviation Ltd.</t>
+  </si>
+  <si>
+    <t>INE646L01027</t>
+  </si>
+  <si>
+    <t>Transport Services</t>
+  </si>
+  <si>
+    <t>SBI Life Insurance Company Ltd.</t>
+  </si>
+  <si>
+    <t>INE123W01016</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>PG Electroplast Ltd.</t>
+  </si>
+  <si>
+    <t>INE457L01029</t>
   </si>
   <si>
     <t>Sun Pharmaceutical Industries Ltd.</t>
@@ -202,33 +235,6 @@
     <t>Pharmaceuticals &amp; Biotechnology</t>
   </si>
   <si>
-    <t>RR Kabel Ltd.</t>
-  </si>
-  <si>
-    <t>INE777K01022</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Interglobe Aviation Ltd.</t>
-  </si>
-  <si>
-    <t>INE646L01027</t>
-  </si>
-  <si>
-    <t>Transport Services</t>
-  </si>
-  <si>
-    <t>SBI Life Insurance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE123W01016</t>
-  </si>
-  <si>
-    <t>Insurance</t>
-  </si>
-  <si>
     <t>Sona Blw Precision Forgings Ltd.</t>
   </si>
   <si>
@@ -244,67 +250,196 @@
     <t>Food Products</t>
   </si>
   <si>
+    <t>Neuland Laboratories Ltd.</t>
+  </si>
+  <si>
+    <t>INE794A01010</t>
+  </si>
+  <si>
+    <t>Sharda Motor Industries Ltd</t>
+  </si>
+  <si>
+    <t>INE597I01028</t>
+  </si>
+  <si>
+    <t>Safari Industries India Ltd</t>
+  </si>
+  <si>
+    <t>INE429E01023</t>
+  </si>
+  <si>
+    <t>Netweb Technologies India</t>
+  </si>
+  <si>
+    <t>INE0NT901020</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>PVR INOX Ltd.</t>
+  </si>
+  <si>
+    <t>INE191H01014</t>
+  </si>
+  <si>
+    <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Ultratech Cement Ltd.</t>
+  </si>
+  <si>
+    <t>INE481G01011</t>
+  </si>
+  <si>
+    <t>Cement &amp; Cement Products</t>
+  </si>
+  <si>
+    <t>Motherson Sumi Wiring India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0FS801015</t>
+  </si>
+  <si>
+    <t>360 One Wam Ltd.</t>
+  </si>
+  <si>
+    <t>INE466L01038</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Rolex Rings Ltd.</t>
+  </si>
+  <si>
+    <t>INE645S01016</t>
+  </si>
+  <si>
+    <t>TBO Tek Ltd.</t>
+  </si>
+  <si>
+    <t>INE673O01025</t>
+  </si>
+  <si>
+    <t>Leisure Services</t>
+  </si>
+  <si>
+    <t>Pearl Global Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE940H01022</t>
+  </si>
+  <si>
+    <t>Textiles &amp; Apparels</t>
+  </si>
+  <si>
+    <t>TVS Holdings Ltd.</t>
+  </si>
+  <si>
+    <t>INE105A01035</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>International Gemmological Institute (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE0Q9301021</t>
+  </si>
+  <si>
+    <t>Commercial Services &amp; Supplies</t>
+  </si>
+  <si>
+    <t>Sundaram Clayton DCD Ltd.</t>
+  </si>
+  <si>
+    <t>INE0Q3R01026</t>
+  </si>
+  <si>
+    <t>Syngene International Ltd.</t>
+  </si>
+  <si>
+    <t>INE398R01022</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Apar Industries Ltd.</t>
+  </si>
+  <si>
+    <t>INE372A01015</t>
+  </si>
+  <si>
+    <t>Cummins India Ltd.</t>
+  </si>
+  <si>
+    <t>INE298A01020</t>
+  </si>
+  <si>
+    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
+  </si>
+  <si>
+    <t>INE703B01027</t>
+  </si>
+  <si>
+    <t>Greenpanel Industries Ltd</t>
+  </si>
+  <si>
+    <t>INE08ZM01014</t>
+  </si>
+  <si>
+    <t>Max Financial Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE180A01020</t>
+  </si>
+  <si>
+    <t>Navin Fluorine International Ltd.</t>
+  </si>
+  <si>
+    <t>INE048G01026</t>
+  </si>
+  <si>
+    <t>Chemicals &amp; Petrochemicals</t>
+  </si>
+  <si>
     <t>HCL Technologies Ltd.</t>
   </si>
   <si>
     <t>INE860A01027</t>
   </si>
   <si>
-    <t>PVR INOX Ltd.</t>
-  </si>
-  <si>
-    <t>INE191H01014</t>
-  </si>
-  <si>
-    <t>Entertainment</t>
-  </si>
-  <si>
-    <t>Sharda Motor Industries Ltd</t>
-  </si>
-  <si>
-    <t>INE597I01028</t>
-  </si>
-  <si>
-    <t>360 One Wam Ltd.</t>
-  </si>
-  <si>
-    <t>INE466L01038</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>Trent Ltd.</t>
-  </si>
-  <si>
-    <t>INE849A01020</t>
-  </si>
-  <si>
-    <t>Safari Industries India Ltd</t>
-  </si>
-  <si>
-    <t>INE429E01023</t>
-  </si>
-  <si>
-    <t>Neuland Laboratories Ltd.</t>
-  </si>
-  <si>
-    <t>INE794A01010</t>
-  </si>
-  <si>
-    <t>PG Electroplast Ltd.</t>
-  </si>
-  <si>
-    <t>INE457L01029</t>
-  </si>
-  <si>
-    <t>Ultratech Cement Ltd.</t>
-  </si>
-  <si>
-    <t>INE481G01011</t>
-  </si>
-  <si>
-    <t>Cement &amp; Cement Products</t>
+    <t>FSN E-Commerce Ventures Ltd.</t>
+  </si>
+  <si>
+    <t>INE388Y01029</t>
+  </si>
+  <si>
+    <t>Tata Consultancy Services Ltd.</t>
+  </si>
+  <si>
+    <t>INE467B01029</t>
+  </si>
+  <si>
+    <t>Siemens Ltd.</t>
+  </si>
+  <si>
+    <t>INE003A01024</t>
+  </si>
+  <si>
+    <t>Century Plyboards (India) Ltd.</t>
+  </si>
+  <si>
+    <t>INE348B01021</t>
+  </si>
+  <si>
+    <t>SIEMENS ENERGY INDIA LTD</t>
+  </si>
+  <si>
+    <t>INE1NPP01017</t>
   </si>
   <si>
     <t>Bharat Forge Ltd.</t>
@@ -313,151 +448,16 @@
     <t>INE465A01025</t>
   </si>
   <si>
-    <t>Aurobindo Pharma Ltd.</t>
-  </si>
-  <si>
-    <t>INE406A01037</t>
-  </si>
-  <si>
-    <t>Zaggle Prepaid Ocean Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE07K301024</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>Syngene International Ltd.</t>
-  </si>
-  <si>
-    <t>INE398R01022</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Navin Fluorine International Ltd.</t>
-  </si>
-  <si>
-    <t>INE048G01026</t>
-  </si>
-  <si>
-    <t>Chemicals &amp; Petrochemicals</t>
-  </si>
-  <si>
-    <t>Siemens Ltd.</t>
-  </si>
-  <si>
-    <t>INE003A01024</t>
-  </si>
-  <si>
-    <t>Greenpanel Industries Ltd</t>
-  </si>
-  <si>
-    <t>INE08ZM01014</t>
-  </si>
-  <si>
-    <t>Motherson Sumi Wiring India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0FS801015</t>
-  </si>
-  <si>
-    <t>Sundaram Clayton DCD Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q3R01026</t>
-  </si>
-  <si>
-    <t>Netweb Technologies India</t>
-  </si>
-  <si>
-    <t>INE0NT901020</t>
-  </si>
-  <si>
-    <t>TBO Tek Ltd.</t>
-  </si>
-  <si>
-    <t>INE673O01025</t>
-  </si>
-  <si>
-    <t>Leisure Services</t>
-  </si>
-  <si>
-    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE703B01027</t>
-  </si>
-  <si>
-    <t>TVS Holdings Ltd.</t>
-  </si>
-  <si>
-    <t>INE105A01035</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Apar Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE372A01015</t>
-  </si>
-  <si>
-    <t>Century Plyboards (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE348B01021</t>
-  </si>
-  <si>
-    <t>Cummins India Ltd.</t>
-  </si>
-  <si>
-    <t>INE298A01020</t>
-  </si>
-  <si>
-    <t>International Gemmological Institute (India) Ltd.</t>
-  </si>
-  <si>
-    <t>INE0Q9301021</t>
-  </si>
-  <si>
-    <t>Commercial Services &amp; Supplies</t>
-  </si>
-  <si>
-    <t>Rolex Rings Ltd.</t>
-  </si>
-  <si>
-    <t>INE645S01016</t>
-  </si>
-  <si>
-    <t>Max Financial Services Ltd.</t>
-  </si>
-  <si>
-    <t>INE180A01020</t>
-  </si>
-  <si>
-    <t>Pearl Global Industries Ltd.</t>
-  </si>
-  <si>
-    <t>INE940H01022</t>
-  </si>
-  <si>
-    <t>Textiles &amp; Apparels</t>
-  </si>
-  <si>
     <t>Mphasis Ltd.</t>
   </si>
   <si>
     <t>INE356A01018</t>
   </si>
   <si>
-    <t>FSN E-Commerce Ventures Ltd.</t>
-  </si>
-  <si>
-    <t>INE388Y01029</t>
+    <t>Chalet Hotels Ltd.</t>
+  </si>
+  <si>
+    <t>INE427F01016</t>
   </si>
   <si>
     <t>Sai Silks (Kalamandir) Ltd.</t>
@@ -472,67 +472,49 @@
     <t>INE01EA01019</t>
   </si>
   <si>
+    <t>LTIMindtree Ltd.</t>
+  </si>
+  <si>
+    <t>INE214T01019</t>
+  </si>
+  <si>
+    <t>Bajaj Electricals Ltd.</t>
+  </si>
+  <si>
+    <t>INE193E01025</t>
+  </si>
+  <si>
+    <t>Ceigall India Ltd.</t>
+  </si>
+  <si>
+    <t>INE0AG901020</t>
+  </si>
+  <si>
+    <t>C.E.Info Systems Ltd.</t>
+  </si>
+  <si>
+    <t>INE0BV301023</t>
+  </si>
+  <si>
+    <t>Ather Energy LTD.</t>
+  </si>
+  <si>
+    <t>INE0LEZ01016</t>
+  </si>
+  <si>
+    <t>G R Infraprojects Ltd.</t>
+  </si>
+  <si>
+    <t>INE201P01022</t>
+  </si>
+  <si>
     <t>Intellect Design Arena Ltd.</t>
   </si>
   <si>
     <t>INE306R01017</t>
   </si>
   <si>
-    <t>Chalet Hotels Ltd.</t>
-  </si>
-  <si>
-    <t>INE427F01016</t>
-  </si>
-  <si>
-    <t>The Phoenix Mills Ltd.</t>
-  </si>
-  <si>
-    <t>INE211B01039</t>
-  </si>
-  <si>
-    <t>Realty</t>
-  </si>
-  <si>
-    <t>LTIMindtree Ltd.</t>
-  </si>
-  <si>
-    <t>INE214T01019</t>
-  </si>
-  <si>
-    <t>Bajaj Electricals Ltd.</t>
-  </si>
-  <si>
-    <t>INE193E01025</t>
-  </si>
-  <si>
-    <t>Ceigall India Ltd.</t>
-  </si>
-  <si>
-    <t>INE0AG901020</t>
-  </si>
-  <si>
-    <t>Go Digit General Insurance Ltd</t>
-  </si>
-  <si>
-    <t>INE03JT01014</t>
-  </si>
-  <si>
-    <t>C.E.Info Systems Ltd.</t>
-  </si>
-  <si>
-    <t>INE0BV301023</t>
-  </si>
-  <si>
-    <t>Standard Glass Lining Technology Ltd</t>
-  </si>
-  <si>
-    <t>INE0M4D01010</t>
-  </si>
-  <si>
-    <t>G R Infraprojects Ltd.</t>
-  </si>
-  <si>
-    <t>INE201P01022</t>
+    <t>^</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -568,13 +550,22 @@
     <t>Treasury Bills</t>
   </si>
   <si>
+    <t>364 Days Treasury Bills</t>
+  </si>
+  <si>
+    <t>IN002024Z198</t>
+  </si>
+  <si>
+    <t>SOV</t>
+  </si>
+  <si>
     <t>91 Days Treasury Bills</t>
   </si>
   <si>
-    <t>IN002024X409</t>
-  </si>
-  <si>
-    <t>SOV</t>
+    <t>IN002024X490</t>
+  </si>
+  <si>
+    <t>IN002024X516</t>
   </si>
   <si>
     <t>Units of Real Estate Investment Trust (REITs)</t>
@@ -598,16 +589,37 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t>Details of Stock Future / Index Future</t>
+  </si>
+  <si>
+    <t>Stock / Index Futures</t>
+  </si>
+  <si>
+    <t>Sona Blw Precision Forgings Ltd. $$</t>
+  </si>
+  <si>
+    <t>Maruti Suzuki India Ltd. $$</t>
+  </si>
+  <si>
+    <t>Note- 1 : Index/ Stock futures are provided towards end of the table.</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
+    <t>$$ - Derivatives.</t>
+  </si>
+  <si>
+    <t>^ Value Less than 0.01% of NAV in absolute terms.</t>
+  </si>
+  <si>
     <t>For the Instrument/security whose final ISIN is yet to be assigned, disclosure of ISIN has been made as per the details provided by external agencies.</t>
   </si>
   <si>
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -619,17 +631,18 @@
     <t>Benchmark Riskometer</t>
   </si>
   <si>
-    <t>Benchmark name - BSE 500 TRI 1</t>
+    <t>Benchmark name - S&amp;P BSE 500 TRI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="177" formatCode="##0.00"/>
     <numFmt numFmtId="178" formatCode="##0.00%"/>
-    <numFmt numFmtId="179" formatCode="##0"/>
+    <numFmt numFmtId="179" formatCode="\^"/>
+    <numFmt numFmtId="180" formatCode="##0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -819,7 +832,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -871,7 +884,7 @@
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection/>
     </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -880,6 +893,10 @@
       <protection/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection/>
     </xf>
@@ -990,13 +1007,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1014,8 +1031,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="23317200"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="25603200"/>
+          <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1029,13 +1046,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>157</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1053,8 +1070,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="26174700"/>
-          <a:ext cx="3571875" cy="1905000"/>
+          <a:off x="666750" y="28460700"/>
+          <a:ext cx="3590925" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1387,19 +1404,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J134"/>
+  <dimension ref="B1:J146"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="34.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="11.142857142857142" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="21" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="21" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="53.857142857142854" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="16.857142857142858" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="34.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="11.142857142857142" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1487,10 +1504,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>1602005.06</v>
+        <v>1679487.3100000003</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9903505388338001</v>
+        <v>0.9606027088183999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1524,10 +1541,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>1602005.06</v>
+        <v>1679487.3100000003</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9903505388338001</v>
+        <v>0.9606027088183999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1550,13 +1567,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="14">
-        <v>6806418</v>
+        <v>6098728</v>
       </c>
       <c r="G8" s="15">
-        <v>167294.95</v>
+        <v>169593.43</v>
       </c>
       <c r="H8" s="16">
-        <v>0.1034207993557</v>
+        <v>0.097000976004</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>13</v>
@@ -1576,16 +1593,16 @@
         <v>13</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F9" s="14">
-        <v>1175045</v>
+        <v>9614694</v>
       </c>
       <c r="G9" s="15">
-        <v>144655.68</v>
+        <v>139009.25</v>
       </c>
       <c r="H9" s="16">
-        <v>0.0894253296764</v>
+        <v>0.0795079911031</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>13</v>
@@ -1596,25 +1613,25 @@
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1">
       <c r="B10" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F10" s="14">
-        <v>9714694</v>
+        <v>1080045</v>
       </c>
       <c r="G10" s="15">
-        <v>121705.69</v>
+        <v>133050.74</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0752377746366</v>
+        <v>0.0760999505585</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1640,10 +1657,10 @@
         <v>2427474</v>
       </c>
       <c r="G11" s="15">
-        <v>88958.43</v>
+        <v>97149.94</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0549936022577</v>
+        <v>0.0555660617202</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1663,16 +1680,16 @@
         <v>13</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" s="14">
         <v>4186743</v>
       </c>
       <c r="G12" s="15">
-        <v>71122.30</v>
+        <v>81427.96</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0439674067748</v>
+        <v>0.0465736885798</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1695,13 +1712,13 @@
         <v>30</v>
       </c>
       <c r="F13" s="14">
-        <v>3153161</v>
+        <v>3653161</v>
       </c>
       <c r="G13" s="15">
-        <v>59273.12</v>
+        <v>57087.95</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0366423101875</v>
+        <v>0.0326521308524</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1724,13 +1741,13 @@
         <v>25</v>
       </c>
       <c r="F14" s="14">
-        <v>24503226</v>
+        <v>23720842</v>
       </c>
       <c r="G14" s="15">
-        <v>53992.86</v>
+        <v>56529.14</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0333780830844</v>
+        <v>0.0323325128377</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1753,13 +1770,13 @@
         <v>35</v>
       </c>
       <c r="F15" s="14">
-        <v>7282126</v>
+        <v>1364660</v>
       </c>
       <c r="G15" s="15">
-        <v>49143.43</v>
+        <v>52180.50</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0303801926698</v>
+        <v>0.0298452565549</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1782,13 +1799,13 @@
         <v>38</v>
       </c>
       <c r="F16" s="14">
-        <v>1306796</v>
+        <v>1720871</v>
       </c>
       <c r="G16" s="15">
-        <v>46618.64</v>
+        <v>49034.50</v>
       </c>
       <c r="H16" s="16">
-        <v>0.028819381659</v>
+        <v>0.0280458644999</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1808,16 +1825,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F17" s="14">
-        <v>831725</v>
+        <v>1273733</v>
       </c>
       <c r="G17" s="15">
-        <v>43202.29</v>
+        <v>46810.96</v>
       </c>
       <c r="H17" s="16">
-        <v>0.026707413259</v>
+        <v>0.0267740843951</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1828,25 +1845,25 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F18" s="14">
-        <v>1669569</v>
+        <v>2498014</v>
       </c>
       <c r="G18" s="15">
-        <v>40593.07</v>
+        <v>44224.84</v>
       </c>
       <c r="H18" s="16">
-        <v>0.025094408096</v>
+        <v>0.0252949223541</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1857,25 +1874,25 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>984668</v>
+        <v>3445838</v>
       </c>
       <c r="G19" s="15">
-        <v>34303.37</v>
+        <v>41081.28</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0212061508491</v>
+        <v>0.0234969258861</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1886,25 +1903,25 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="F20" s="14">
-        <v>3391318</v>
+        <v>2131461</v>
       </c>
       <c r="G20" s="15">
-        <v>33441.79</v>
+        <v>39564.18</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0206735269276</v>
+        <v>0.0226292025274</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1915,25 +1932,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F21" s="14">
-        <v>2031461</v>
+        <v>29228504</v>
       </c>
       <c r="G21" s="15">
-        <v>33037.65</v>
+        <v>39210.04</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0204236898474</v>
+        <v>0.0224266479494</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1944,25 +1961,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F22" s="14">
-        <v>3905935</v>
+        <v>2447540</v>
       </c>
       <c r="G22" s="15">
-        <v>30188.97</v>
+        <v>34894.58</v>
       </c>
       <c r="H22" s="16">
-        <v>0.018662651856</v>
+        <v>0.0199583693616</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1973,25 +1990,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F23" s="14">
-        <v>21174521</v>
+        <v>633429</v>
       </c>
       <c r="G23" s="15">
-        <v>29911.13</v>
+        <v>33783.94</v>
       </c>
       <c r="H23" s="16">
-        <v>0.018490892727</v>
+        <v>0.0193231256261</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2002,25 +2019,25 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24" s="14">
-        <v>1672140</v>
+        <v>21174521</v>
       </c>
       <c r="G24" s="15">
-        <v>25910.65</v>
+        <v>32422.43</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0160178184387</v>
+        <v>0.0185443938153</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2031,25 +2048,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F25" s="14">
-        <v>1481237</v>
+        <v>3936413</v>
       </c>
       <c r="G25" s="15">
-        <v>25832.03</v>
+        <v>31975.48</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0159692159959</v>
+        <v>0.0182887554558</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2072,13 +2089,13 @@
         <v>64</v>
       </c>
       <c r="F26" s="14">
-        <v>2016669</v>
+        <v>590299</v>
       </c>
       <c r="G26" s="15">
-        <v>24724.36</v>
+        <v>31462.94</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0152844606173</v>
+        <v>0.0179956021171</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2101,13 +2118,13 @@
         <v>67</v>
       </c>
       <c r="F27" s="14">
-        <v>555299</v>
+        <v>1487149</v>
       </c>
       <c r="G27" s="15">
-        <v>24013.07</v>
+        <v>26950.11</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0148447451306</v>
+        <v>0.0154144354142</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2127,16 +2144,16 @@
         <v>13</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F28" s="14">
-        <v>1487149</v>
+        <v>3459030</v>
       </c>
       <c r="G28" s="15">
-        <v>22063.34</v>
+        <v>26684.69</v>
       </c>
       <c r="H28" s="16">
-        <v>0.013639432985</v>
+        <v>0.0152626252937</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2147,25 +2164,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>55</v>
-      </c>
       <c r="F29" s="14">
-        <v>4212362</v>
+        <v>1581237</v>
       </c>
       <c r="G29" s="15">
-        <v>21242.94</v>
+        <v>26526.83</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0131322663084</v>
+        <v>0.0151723353923</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2185,16 +2202,16 @@
         <v>13</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F30" s="14">
-        <v>374118</v>
+        <v>4585490</v>
       </c>
       <c r="G30" s="15">
-        <v>19190.94</v>
+        <v>24942.77</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0118637314227</v>
+        <v>0.0142663134665</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2205,25 +2222,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>30</v>
-      </c>
       <c r="F31" s="14">
-        <v>1042649</v>
+        <v>416818</v>
       </c>
       <c r="G31" s="15">
-        <v>17990.39</v>
+        <v>22968.76</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0111215581493</v>
+        <v>0.013137255008</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2243,16 +2260,16 @@
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F32" s="14">
-        <v>1530838</v>
+        <v>197943</v>
       </c>
       <c r="G32" s="15">
-        <v>16693.79</v>
+        <v>22769.38</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0103200073049</v>
+        <v>0.0130232172496</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2263,25 +2280,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F33" s="14">
-        <v>926375</v>
+        <v>980981</v>
       </c>
       <c r="G33" s="15">
-        <v>16579.80</v>
+        <v>18671.99</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0102495393265</v>
+        <v>0.0106796663876</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2292,25 +2309,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>84</v>
-      </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="F34" s="14">
-        <v>1639576</v>
+        <v>799865</v>
       </c>
       <c r="G34" s="15">
-        <v>16522.83</v>
+        <v>18458.48</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0102143207922</v>
+        <v>0.0105575468079</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2321,25 +2338,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>25</v>
-      </c>
       <c r="F35" s="14">
-        <v>285798</v>
+        <v>795278</v>
       </c>
       <c r="G35" s="15">
-        <v>16442.53</v>
+        <v>15898.40</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0101646797828</v>
+        <v>0.0090932786541</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2350,25 +2367,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="F36" s="14">
-        <v>681838</v>
+        <v>1530838</v>
       </c>
       <c r="G36" s="15">
-        <v>16432.30</v>
+        <v>15082.58</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0101583556542</v>
+        <v>0.0086266607182</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2388,16 +2405,16 @@
         <v>13</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="F37" s="14">
-        <v>109675</v>
+        <v>125323</v>
       </c>
       <c r="G37" s="15">
-        <v>15489.78</v>
+        <v>14048.71</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0095756950789</v>
+        <v>0.0080353264958</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2408,25 +2425,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F38" s="14">
-        <v>1967253</v>
+        <v>23073418</v>
       </c>
       <c r="G38" s="15">
-        <v>15393.75</v>
+        <v>13354.89</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0095163298717</v>
+        <v>0.0076384879085</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2437,25 +2454,25 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D39" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F39" s="14">
-        <v>122438</v>
+        <v>1304848</v>
       </c>
       <c r="G39" s="15">
-        <v>14065</v>
+        <v>13015.21</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0086949040777</v>
+        <v>0.0074442038992</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2466,25 +2483,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F40" s="14">
-        <v>1101218</v>
+        <v>753936</v>
       </c>
       <c r="G40" s="15">
-        <v>13479.46</v>
+        <v>12084.84</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0083329265353</v>
+        <v>0.0069120677307</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2495,25 +2512,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="F41" s="14">
-        <v>1140371</v>
+        <v>913226</v>
       </c>
       <c r="G41" s="15">
-        <v>13364.01</v>
+        <v>11914.86</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0082615559931</v>
+        <v>0.0068148456514</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2524,25 +2541,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F42" s="14">
-        <v>2995216</v>
+        <v>803769</v>
       </c>
       <c r="G42" s="15">
-        <v>13238.85</v>
+        <v>11702.88</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0081841827834</v>
+        <v>0.0066936011734</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2553,25 +2570,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D43" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F43" s="14">
-        <v>1699897</v>
+        <v>96603</v>
       </c>
       <c r="G43" s="15">
-        <v>12692.28</v>
+        <v>11461.46</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0078462962764</v>
+        <v>0.0065555181378</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2582,25 +2599,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F44" s="14">
-        <v>304229</v>
+        <v>2927917</v>
       </c>
       <c r="G44" s="15">
-        <v>12621.55</v>
+        <v>11386.67</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0078025713872</v>
+        <v>0.0065127411093</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2611,25 +2628,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D45" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F45" s="14">
-        <v>206151</v>
+        <v>453145</v>
       </c>
       <c r="G45" s="15">
-        <v>12520.27</v>
+        <v>11226.67</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0077399606596</v>
+        <v>0.0064212272095</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2640,25 +2657,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D46" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="F46" s="14">
-        <v>3454178</v>
+        <v>1699897</v>
       </c>
       <c r="G46" s="15">
-        <v>12037.81</v>
+        <v>10990.68</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0074417065948</v>
+        <v>0.0062862499269</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2669,25 +2686,25 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F47" s="14">
-        <v>21073418</v>
+        <v>130941</v>
       </c>
       <c r="G47" s="15">
-        <v>11828.51</v>
+        <v>10624.55</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0073123185092</v>
+        <v>0.006076837526</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2698,25 +2715,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F48" s="14">
-        <v>496838</v>
+        <v>304661</v>
       </c>
       <c r="G48" s="15">
-        <v>10768.96</v>
+        <v>9956.63</v>
       </c>
       <c r="H48" s="16">
-        <v>0.0066573106446</v>
+        <v>0.0056948127513</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2727,25 +2744,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="F49" s="14">
-        <v>593650</v>
+        <v>332292</v>
       </c>
       <c r="G49" s="15">
-        <v>10650.38</v>
+        <v>9433.77</v>
       </c>
       <c r="H49" s="16">
-        <v>0.006584005154</v>
+        <v>0.005395756766</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2756,25 +2773,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D50" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="F50" s="14">
-        <v>644192</v>
+        <v>3654178</v>
       </c>
       <c r="G50" s="15">
-        <v>10037.16</v>
+        <v>9323.27</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0062049159909</v>
+        <v>0.0053325549789</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2785,25 +2802,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D51" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F51" s="14">
-        <v>332292</v>
+        <v>600722</v>
       </c>
       <c r="G51" s="15">
-        <v>9498.90</v>
+        <v>9027.05</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0058721666792</v>
+        <v>0.0051631284327</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2814,25 +2831,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F52" s="14">
-        <v>96944</v>
+        <v>202987</v>
       </c>
       <c r="G52" s="15">
-        <v>9076.53</v>
+        <v>8649.68</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0056110599152</v>
+        <v>0.0049472871804</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2843,25 +2860,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F53" s="14">
-        <v>100941</v>
+        <v>495606</v>
       </c>
       <c r="G53" s="15">
-        <v>7562.45</v>
+        <v>8111.09</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0046750641551</v>
+        <v>0.0046392342348</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2872,25 +2889,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F54" s="14">
-        <v>924185</v>
+        <v>3780126</v>
       </c>
       <c r="G54" s="15">
-        <v>7436.45</v>
+        <v>7683.48</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0045971716622</v>
+        <v>0.0043946576179</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2901,25 +2918,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="F55" s="14">
-        <v>254661</v>
+        <v>200000</v>
       </c>
       <c r="G55" s="15">
-        <v>7420.95</v>
+        <v>6926.80</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0045875896491</v>
+        <v>0.0039618655073</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2930,25 +2947,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="F56" s="14">
-        <v>1384925</v>
+        <v>206151</v>
       </c>
       <c r="G56" s="15">
-        <v>7016.03</v>
+        <v>6732.07</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0043372703772</v>
+        <v>0.0038504873716</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2959,25 +2976,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F57" s="14">
-        <v>376376</v>
+        <v>740547</v>
       </c>
       <c r="G57" s="15">
-        <v>6768.37</v>
+        <v>5760.72</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0041841683549</v>
+        <v>0.0032949122055</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -2988,25 +3005,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="F58" s="14">
-        <v>600722</v>
+        <v>206151</v>
       </c>
       <c r="G58" s="15">
-        <v>6702.56</v>
+        <v>5108.73</v>
       </c>
       <c r="H58" s="16">
-        <v>0.0041434849822</v>
+        <v>0.0029219987834</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3017,25 +3034,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="F59" s="14">
-        <v>467892</v>
+        <v>379870</v>
       </c>
       <c r="G59" s="15">
-        <v>6615.99</v>
+        <v>4713.81</v>
       </c>
       <c r="H59" s="16">
-        <v>0.004089967894</v>
+        <v>0.0026961196002</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3061,10 +3078,10 @@
         <v>164081</v>
       </c>
       <c r="G60" s="15">
-        <v>4705.76</v>
+        <v>4198.50</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0029090744267</v>
+        <v>0.002401381927</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3084,16 +3101,16 @@
         <v>13</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>25</v>
+        <v>102</v>
       </c>
       <c r="F61" s="14">
-        <v>2780126</v>
+        <v>412250</v>
       </c>
       <c r="G61" s="15">
-        <v>4695.63</v>
+        <v>3783.22</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0029028121176</v>
+        <v>0.0021638576001</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3119,10 +3136,10 @@
         <v>2692738</v>
       </c>
       <c r="G62" s="15">
-        <v>4556.65</v>
+        <v>3423.55</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0028168954614</v>
+        <v>0.0019581400729</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3145,13 +3162,13 @@
         <v>25</v>
       </c>
       <c r="F63" s="14">
-        <v>4105150</v>
+        <v>2709614</v>
       </c>
       <c r="G63" s="15">
-        <v>4431.51</v>
+        <v>3377.80</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0027395346156</v>
+        <v>0.0019319728172</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3174,13 +3191,13 @@
         <v>30</v>
       </c>
       <c r="F64" s="14">
-        <v>545654</v>
+        <v>49508</v>
       </c>
       <c r="G64" s="15">
-        <v>4425.25</v>
+        <v>2509.51</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0027356647188</v>
+        <v>0.0014353440418</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3200,16 +3217,16 @@
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="F65" s="14">
-        <v>487792</v>
+        <v>349571</v>
       </c>
       <c r="G65" s="15">
-        <v>3760.63</v>
+        <v>2400.50</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0023248003641</v>
+        <v>0.001372994478</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3229,16 +3246,16 @@
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>158</v>
+        <v>41</v>
       </c>
       <c r="F66" s="14">
-        <v>202823</v>
+        <v>911596</v>
       </c>
       <c r="G66" s="15">
-        <v>3329.95</v>
+        <v>2277.62</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0020585564048</v>
+        <v>0.0013027118029</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3249,10 +3266,10 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C67" s="13" t="s">
         <v>159</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
@@ -3261,13 +3278,13 @@
         <v>30</v>
       </c>
       <c r="F67" s="14">
-        <v>49508</v>
+        <v>96251</v>
       </c>
       <c r="G67" s="15">
-        <v>2927.98</v>
+        <v>1863.61</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0018100608063</v>
+        <v>0.0010659138675</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3278,25 +3295,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C68" s="13" t="s">
-        <v>162</v>
-      </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F68" s="14">
-        <v>411327</v>
+        <v>506927</v>
       </c>
       <c r="G68" s="15">
-        <v>2881.76</v>
+        <v>1586.68</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0017814878617</v>
+        <v>0.0009075204658</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3307,25 +3324,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C69" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F69" s="14">
-        <v>911596</v>
+        <v>101186</v>
       </c>
       <c r="G69" s="15">
-        <v>2786.75</v>
+        <v>1294.98</v>
       </c>
       <c r="H69" s="16">
-        <v>0.0017227532128</v>
+        <v>0.0007406791873</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3336,25 +3353,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="C70" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="D70" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" s="14">
+        <v>7228</v>
+      </c>
+      <c r="G70" s="15">
+        <v>84.75</v>
+      </c>
+      <c r="H70" s="17" t="s">
         <v>166</v>
-      </c>
-      <c r="D70" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F70" s="14">
-        <v>620684</v>
-      </c>
-      <c r="G70" s="15">
-        <v>1847.78</v>
-      </c>
-      <c r="H70" s="16">
-        <v>0.0011422872276</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3365,56 +3382,35 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F71" s="14">
-        <v>96251</v>
-      </c>
-      <c r="G71" s="15">
-        <v>1637.61</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0010123613129</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E72" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F72" s="14">
-        <v>803570</v>
-      </c>
-      <c r="G72" s="15">
-        <v>1354.18</v>
-      </c>
-      <c r="H72" s="16">
-        <v>0.0008371464773</v>
-      </c>
-      <c r="I72" s="15" t="s">
+      <c r="H72" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I72" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J72" s="11" t="s">
@@ -3423,398 +3419,398 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C73" s="13" t="s">
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="F73" s="14">
-        <v>101186</v>
-      </c>
-      <c r="G73" s="15">
-        <v>1295.28</v>
-      </c>
-      <c r="H73" s="16">
-        <v>0.0008007348278</v>
-      </c>
-      <c r="I73" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="7" t="s">
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9" t="s">
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H75" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9">
+        <v>3472.36</v>
+      </c>
+      <c r="H86" s="10">
+        <v>0.0019860575318</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1">
+      <c r="B91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9">
+        <v>3472.36</v>
+      </c>
+      <c r="H92" s="10">
+        <v>0.0019860575318</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
+      <c r="C93" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
+      <c r="D93" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9">
-        <v>1481.99</v>
-      </c>
-      <c r="H89" s="10">
-        <v>0.0009161579021</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>13</v>
+      <c r="F93" s="14">
+        <v>2500000</v>
+      </c>
+      <c r="G93" s="15">
+        <v>2474.51</v>
+      </c>
+      <c r="H93" s="16">
+        <v>0.0014153253762</v>
+      </c>
+      <c r="I93" s="15">
+        <v>5.61</v>
       </c>
       <c r="J93" s="11" t="s">
         <v>13</v>
@@ -3822,36 +3818,57 @@
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
       <c r="B94" s="12" t="s">
-        <v>13</v>
+        <v>181</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F94" s="14">
+        <v>800000</v>
+      </c>
+      <c r="G94" s="15">
+        <v>798.63</v>
+      </c>
+      <c r="H94" s="16">
+        <v>0.0004567859112</v>
+      </c>
+      <c r="I94" s="15">
+        <v>5.70</v>
       </c>
       <c r="J94" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C95" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9">
-        <v>1481.99</v>
-      </c>
-      <c r="H95" s="10">
-        <v>0.0009161579021</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>13</v>
+      <c r="D95" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="F95" s="14">
+        <v>200000</v>
+      </c>
+      <c r="G95" s="15">
+        <v>199.22</v>
+      </c>
+      <c r="H95" s="16">
+        <v>0.0001139462444</v>
+      </c>
+      <c r="I95" s="15">
+        <v>5.70</v>
       </c>
       <c r="J95" s="11" t="s">
         <v>13</v>
@@ -3859,175 +3876,168 @@
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
       <c r="B96" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="15" customHeight="1">
+      <c r="B97" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15" customHeight="1">
+      <c r="B98" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" ht="15" customHeight="1">
+      <c r="B99" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E96" s="13" t="s">
+      <c r="C99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15" customHeight="1">
+      <c r="B100" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="2:10" ht="15" customHeight="1">
+      <c r="B101" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="F96" s="14">
-        <v>1500000</v>
-      </c>
-      <c r="G96" s="15">
-        <v>1481.99</v>
-      </c>
-      <c r="H96" s="16">
-        <v>0.0009161579021</v>
-      </c>
-      <c r="I96" s="15">
-        <v>6.52</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="7" t="s">
+      <c r="C101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G101" s="9">
+        <v>64088.82</v>
+      </c>
+      <c r="H101" s="10">
+        <v>0.0366563615757</v>
+      </c>
+      <c r="I101" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J101" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="2:10" ht="15" customHeight="1">
+      <c r="B102" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:10" ht="15" customHeight="1">
+      <c r="B103" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G98" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H98" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I98" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="7" t="s">
+      <c r="C103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G103" s="9">
+        <v>3055.11731</v>
+      </c>
+      <c r="H103" s="10">
+        <v>0.0017474106212</v>
+      </c>
+      <c r="I103" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J103" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="2:10" ht="15" customHeight="1">
+      <c r="B104" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G100" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H100" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="I100" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J101" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="9">
-        <v>16331.34</v>
-      </c>
-      <c r="H102" s="10">
-        <v>0.0100959427487</v>
-      </c>
-      <c r="I102" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J103" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F104" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="9">
-        <v>255.11731</v>
-      </c>
-      <c r="H104" s="10">
-        <v>0.0001577120895</v>
-      </c>
-      <c r="I104" s="9" t="s">
+      <c r="C104" s="13"/>
+      <c r="D104" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="13"/>
+      <c r="G104" s="15">
+        <v>3055.11731</v>
+      </c>
+      <c r="H104" s="16">
+        <v>0.0017474106212</v>
+      </c>
+      <c r="I104" s="15" t="s">
         <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
@@ -4036,173 +4046,311 @@
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
       <c r="B105" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="2:10" ht="15" customHeight="1">
+      <c r="B106" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="19">
+        <v>-1735.3229231098667</v>
+      </c>
+      <c r="H106" s="20">
+        <v>-0.0009925385507198227</v>
+      </c>
+      <c r="I106" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J106" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="2:10" ht="15" customHeight="1">
+      <c r="B107" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G107" s="19">
+        <v>1748368.28438689</v>
+      </c>
+      <c r="H107" s="20">
+        <v>0.9999999999963801</v>
+      </c>
+      <c r="I107" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="2:8" ht="15" customHeight="1">
+      <c r="B109" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="C105" s="13"/>
-      <c r="D105" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="13"/>
-      <c r="G105" s="15">
-        <v>255.11731</v>
-      </c>
-      <c r="H105" s="16">
-        <v>0.0001577120895</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J105" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J106" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="17" t="s">
+      <c r="C109" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D109" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G109" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8" ht="15" customHeight="1">
+      <c r="B110" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D110" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="G110" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H110" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8" ht="15" customHeight="1">
+      <c r="B111" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C107" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="18">
-        <v>-2459.3422476099804</v>
-      </c>
-      <c r="H107" s="19">
-        <v>-0.001520351577482091</v>
-      </c>
-      <c r="I107" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="17" t="s">
+      <c r="C111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="2:10" ht="15" customHeight="1">
+      <c r="B112" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C108" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D108" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E108" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G108" s="18">
-        <v>1617614.16506239</v>
-      </c>
-      <c r="H108" s="19">
-        <v>0.9999999999966179</v>
-      </c>
-      <c r="I108" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J108" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="2:9" ht="15" customHeight="1">
-      <c r="B111" s="13" t="s">
+      <c r="C112" s="13"/>
+      <c r="D112" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F112" s="14">
+        <v>1074150</v>
+      </c>
+      <c r="G112" s="15">
+        <v>5788.06</v>
+      </c>
+      <c r="H112" s="16">
+        <v>0.0033105496431</v>
+      </c>
+      <c r="I112" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J112" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="2:10" ht="15" customHeight="1">
+      <c r="B113" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C111" s="21"/>
-      <c r="D111" s="21"/>
-      <c r="E111" s="21"/>
-      <c r="F111" s="21"/>
-      <c r="G111" s="21"/>
-      <c r="H111" s="21"/>
-      <c r="I111" s="21"/>
-    </row>
-    <row r="112" spans="2:8" ht="15" customHeight="1">
-      <c r="B112" s="13" t="s">
+      <c r="C113" s="13"/>
+      <c r="D113" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F113" s="14">
+        <v>-50000</v>
+      </c>
+      <c r="G113" s="15">
+        <v>-6165</v>
+      </c>
+      <c r="H113" s="16">
+        <v>-0.0035261449518</v>
+      </c>
+      <c r="I113" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J113" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" ht="15" customHeight="1">
+      <c r="B117" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C112" s="21"/>
-      <c r="D112" s="21"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="21"/>
-      <c r="H112" s="21"/>
-    </row>
-    <row r="113" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B113" s="22" t="s">
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="22"/>
+      <c r="I117" s="22"/>
+    </row>
+    <row r="121" spans="2:9" ht="15" customHeight="1">
+      <c r="B121" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C113" s="21"/>
-      <c r="D113" s="21"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="21"/>
-      <c r="H113" s="21"/>
-    </row>
-    <row r="114" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B114" s="22" t="s">
+      <c r="C121" s="22"/>
+      <c r="D121" s="22"/>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22"/>
+      <c r="G121" s="22"/>
+      <c r="H121" s="22"/>
+      <c r="I121" s="22"/>
+    </row>
+    <row r="122" spans="2:8" ht="15" customHeight="1">
+      <c r="B122" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="C114" s="21"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="21"/>
-      <c r="F114" s="21"/>
-      <c r="G114" s="21"/>
-      <c r="H114" s="21"/>
-    </row>
-    <row r="115" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B115" s="22" t="s">
+      <c r="C122" s="22"/>
+      <c r="D122" s="22"/>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22"/>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22"/>
+    </row>
+    <row r="123" spans="2:8" ht="15" customHeight="1">
+      <c r="B123" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="21"/>
-      <c r="F115" s="21"/>
-      <c r="G115" s="21"/>
-      <c r="H115" s="21"/>
-    </row>
-    <row r="118" ht="15">
-      <c r="B118" s="21" t="s">
+      <c r="C123" s="22"/>
+      <c r="D123" s="22"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22"/>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22"/>
+    </row>
+    <row r="124" spans="2:8" ht="15" customHeight="1">
+      <c r="B124" s="13" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="133" ht="15">
-      <c r="B133" s="21" t="s">
+      <c r="C124" s="22"/>
+      <c r="D124" s="22"/>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22"/>
+      <c r="G124" s="22"/>
+      <c r="H124" s="22"/>
+    </row>
+    <row r="125" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B125" s="23" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="134" ht="15">
-      <c r="B134" s="21" t="s">
+      <c r="C125" s="22"/>
+      <c r="D125" s="22"/>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22"/>
+      <c r="G125" s="22"/>
+      <c r="H125" s="22"/>
+    </row>
+    <row r="126" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B126" s="23" t="s">
         <v>201</v>
       </c>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
+      <c r="G126" s="22"/>
+      <c r="H126" s="22"/>
+    </row>
+    <row r="127" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B127" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
+      <c r="G127" s="22"/>
+      <c r="H127" s="22"/>
+    </row>
+    <row r="130" ht="15">
+      <c r="B130" s="22" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="145" ht="15">
+      <c r="B145" s="22" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="146" ht="15">
+      <c r="B146" s="22" t="s">
+        <v>205</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B113:H113"/>
-    <mergeCell ref="B114:H114"/>
-    <mergeCell ref="B115:H115"/>
+  <mergeCells count="11">
+    <mergeCell ref="B127:H127"/>
+    <mergeCell ref="B122:H122"/>
+    <mergeCell ref="B123:H123"/>
+    <mergeCell ref="B124:H124"/>
+    <mergeCell ref="B125:H125"/>
+    <mergeCell ref="B126:H126"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B111:I111"/>
-    <mergeCell ref="B112:H112"/>
+    <mergeCell ref="B117:I117"/>
+    <mergeCell ref="B121:I121"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
